--- a/doanmon/FILE_LOI_5_TAT_CA_LOI.xlsx
+++ b/doanmon/FILE_LOI_5_TAT_CA_LOI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
   <si>
     <t>productCode</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Empty ProductCode</t>
   </si>
   <si>
-    <t>Chocolate</t>
+    <t>Birthday Cakes</t>
   </si>
   <si>
     <t>ERROR: productCode is empty</t>
@@ -47,7 +47,7 @@
     <t>CAKE-001</t>
   </si>
   <si>
-    <t>Vanilla</t>
+    <t>Wedding Cakes</t>
   </si>
   <si>
     <t>ERROR: name is empty</t>
@@ -59,7 +59,7 @@
     <t>Negative Price</t>
   </si>
   <si>
-    <t>Fruit</t>
+    <t>Cheese Cakes</t>
   </si>
   <si>
     <t>ERROR: price is negative</t>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>Bad Quantity</t>
+  </si>
+  <si>
+    <t>Gataux</t>
   </si>
   <si>
     <t>abc</t>
@@ -311,13 +314,13 @@
         <v>22.5</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
@@ -325,7 +328,7 @@
         <v>10</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="n" s="0">
         <v>19.99</v>
@@ -337,87 +340,87 @@
         <v>10.0</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n" s="0">
         <v>24.99</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E8" t="n" s="0">
         <v>25.0</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n" s="0">
         <v>30.0</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n" s="0">
         <v>5.0</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n" s="0">
         <v>10.0</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n" s="0">
         <v>25.99</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E11" t="n" s="0">
         <v>-5.0</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
